--- a/Backend/Input/ADP/Planilla ADP monitoreo.xlsx
+++ b/Backend/Input/ADP/Planilla ADP monitoreo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mineduca.sharepoint.com/sites/PCG/Documentos compartidos/Reporte mensual -ATMM/ADP/2024/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mineduca.sharepoint.com/sites/PCG/Documentos compartidos/Reporte mensual -ATMM/ADP/2025/Febrero/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="8_{50EE1512-5B22-4D40-BDDF-5CEBD82B5728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2E02420-7279-4E4A-BDAC-5289AE576D1B}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{437B6267-DA54-4829-A3BA-980E850D581E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFBA8CFA-ABEB-4299-BCE9-4A9CFC8E18FF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4A0AD951-A275-4FB5-B4BD-A57A3ECB8FBA}"/>
   </bookViews>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,12 +34,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="26">
   <si>
     <t>Servicio</t>
   </si>
   <si>
-    <t>Convenio totalmente tramitado</t>
+    <t>Fecha Nombramiento</t>
   </si>
   <si>
     <t>Monitoreo Año 1</t>
@@ -83,25 +81,37 @@
     <t>Superintendencia de Educación Superior</t>
   </si>
   <si>
+    <t>SLEP Gabriela Mistral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLEP Chiloé </t>
+  </si>
+  <si>
     <t>Comentarios</t>
   </si>
   <si>
-    <t>En diciembre se inició el monitoreo del tercer año de gestión.</t>
-  </si>
-  <si>
-    <t>En noviembre se tramitó totalmente el acto administrativo que aprueba el grado de cumplimiento global de las metas del convenio.</t>
-  </si>
-  <si>
-    <t>En diciembre se envió a tramitación el acto administrativo que aprueba el grado de cumplimiento global de las metas del convenio.</t>
-  </si>
-  <si>
-    <t>En noviembre se inició el monitoreo del primer año de gestión. En diciembre DEP informa que el Director se encuentra con licencia médica hasta 19.01.25. Además, informa que una vez el Director se reincorpore a sus funciones, realizarán el procedimiento y remitirán los antecedentes ya que ,de acuerdo a lo señalado por Servicio Civil, el convenio es un instrumento personal e intransferible.</t>
-  </si>
-  <si>
-    <t>En agosto se envió mediante mail del Jefe del Gabinete del Ministro, el resultado del monitoreo del segundo año de gestión.</t>
-  </si>
-  <si>
-    <t>En octubre se envió mediante mail del Jefe del Gabinete del Ministro, el resultado del monitoreo del segundo año de gestión.</t>
+    <t>En enero 2025 se tramitó totalmente el acto administrativo que aprueba el grado de cumplimiento global de las metas del convenio del 1er año de gestión.</t>
+  </si>
+  <si>
+    <t>En enero 2025 se tramitó totalmente el acto administrativo que aprueba el convenio del Jefe de Planificación y Control de Gestión del SLEP Chiloé. Esto se realizó ante la ausencia de un Director del SLEP nombrado a la fecha del acto administrativo.</t>
+  </si>
+  <si>
+    <t>En enero 2025 se envió mediante mail del Jefe del Gabinete del Ministro, el resultado del monitoreo del tercer año de gestión.</t>
+  </si>
+  <si>
+    <t>En febrero 2025 se inició el monitoreo del tercer año de gestión.</t>
+  </si>
+  <si>
+    <t>En enero 2025 se tramitó totalmente el acto administrativo que aprueba el grado de cumplimiento global de las metas del convenio del 2do año de gestión.</t>
+  </si>
+  <si>
+    <t>En noviembre 2024 se inició el monitoreo del primer año de gestión. En diciembre DEP informa que el Director se encuentra con licencia médica, la cual se ha extendido hasta el mes de febrero.</t>
+  </si>
+  <si>
+    <t>En febrero 2025 se tramitó totalmente el acto administrativo que aprueba el grado de cumplimiento global de las metas del convenio del 2do año de gestión.</t>
+  </si>
+  <si>
+    <t>En febrero 2025 se inició el monitoreo del segundo año de gestión.</t>
   </si>
 </sst>
 </file>
@@ -117,18 +127,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="18"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
+      <sz val="14"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="14"/>
@@ -138,18 +145,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Aptos Narrow"/>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="Calibri Light"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="14"/>
+      <color rgb="FF000000"/>
       <name val="Calibri Light"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -168,26 +176,25 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAF2D0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="18">
+  <borders count="19">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -231,82 +238,6 @@
         <color indexed="64"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -357,17 +288,41 @@
     </border>
     <border>
       <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color theme="1"/>
       </left>
       <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
         <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -377,12 +332,10 @@
       <right style="thin">
         <color theme="1"/>
       </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1"/>
-      </bottom>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -390,85 +343,180 @@
         <color theme="1"/>
       </left>
       <right style="medium">
-        <color theme="1"/>
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color theme="1"/>
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
       </top>
       <bottom style="medium">
-        <color theme="1"/>
+        <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="1" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="5" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -485,6 +533,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -804,315 +856,375 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0C29CBF-8F22-456D-B3FB-D5E8EA4BA277}">
-  <dimension ref="B3:I23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A3:I24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="52" customWidth="1"/>
-    <col min="3" max="3" width="36.7109375" customWidth="1"/>
-    <col min="4" max="4" width="25.42578125" customWidth="1"/>
-    <col min="5" max="5" width="25.85546875" customWidth="1"/>
-    <col min="6" max="6" width="24.140625" customWidth="1"/>
-    <col min="7" max="7" width="25" customWidth="1"/>
-    <col min="8" max="8" width="23.5703125" customWidth="1"/>
-    <col min="9" max="9" width="26.28515625" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" style="11"/>
+    <col min="2" max="2" width="52" style="11" customWidth="1"/>
+    <col min="3" max="3" width="36.7109375" style="11" customWidth="1"/>
+    <col min="4" max="4" width="25.42578125" style="11" customWidth="1"/>
+    <col min="5" max="5" width="25.85546875" style="11" customWidth="1"/>
+    <col min="6" max="6" width="24.140625" style="11" customWidth="1"/>
+    <col min="7" max="7" width="25" style="11" customWidth="1"/>
+    <col min="8" max="8" width="23.5703125" style="11" customWidth="1"/>
+    <col min="9" max="9" width="26.28515625" style="11" customWidth="1"/>
+    <col min="10" max="16384" width="11.42578125" style="12"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="2:9" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="8" t="s">
+    <row r="3" spans="2:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="2:9" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="15" t="s">
+      <c r="I4" s="17" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="21" x14ac:dyDescent="0.25">
-      <c r="B5" s="9" t="s">
+    <row r="5" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="17">
-        <v>44725</v>
-      </c>
-      <c r="D5" s="17">
+      <c r="C5" s="4">
+        <v>44728</v>
+      </c>
+      <c r="D5" s="4">
         <v>44908</v>
       </c>
-      <c r="E5" s="17">
-        <v>45093</v>
-      </c>
-      <c r="F5" s="17">
+      <c r="E5" s="4">
+        <v>45090</v>
+      </c>
+      <c r="F5" s="4">
         <v>45273</v>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="4">
         <v>45456</v>
       </c>
-      <c r="H5" s="17">
+      <c r="H5" s="4">
         <v>45639</v>
       </c>
-      <c r="I5" s="19">
+      <c r="I5" s="5">
         <v>45821</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="21" x14ac:dyDescent="0.25">
-      <c r="B6" s="10" t="s">
+    <row r="6" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="17">
-        <v>37484</v>
-      </c>
-      <c r="D6" s="17">
+      <c r="C6" s="1">
+        <v>44789</v>
+      </c>
+      <c r="D6" s="1">
         <v>44608</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="1">
         <v>45154</v>
       </c>
-      <c r="F6" s="17">
+      <c r="F6" s="1">
         <v>45338</v>
       </c>
-      <c r="G6" s="17">
+      <c r="G6" s="1">
         <v>45520</v>
       </c>
-      <c r="H6" s="18">
+      <c r="H6" s="2">
         <v>45704</v>
       </c>
-      <c r="I6" s="19">
+      <c r="I6" s="6">
         <v>45885</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="21" x14ac:dyDescent="0.25">
-      <c r="B7" s="10" t="s">
+    <row r="7" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="1">
         <v>44868</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="1">
         <v>45049</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="1">
         <v>45233</v>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="1">
         <v>45415</v>
       </c>
-      <c r="G7" s="18">
+      <c r="G7" s="2">
         <v>45599</v>
       </c>
-      <c r="H7" s="18">
+      <c r="H7" s="3">
         <v>45780</v>
       </c>
-      <c r="I7" s="19">
+      <c r="I7" s="6">
         <v>45964</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="21" x14ac:dyDescent="0.25">
-      <c r="B8" s="10" t="s">
+    <row r="8" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="1">
         <v>45439</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="1">
         <v>45623</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="3">
         <v>45804</v>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="3">
         <v>45988</v>
       </c>
-      <c r="G8" s="18">
+      <c r="G8" s="3">
         <v>46169</v>
       </c>
-      <c r="H8" s="18">
+      <c r="H8" s="3">
         <v>46353</v>
       </c>
-      <c r="I8" s="19">
+      <c r="I8" s="6">
         <v>46534</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="21" x14ac:dyDescent="0.25">
-      <c r="B9" s="10" t="s">
+    <row r="9" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="1">
         <v>44900</v>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="1">
         <v>45082</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="1">
         <v>45265</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="1">
         <v>45448</v>
       </c>
-      <c r="G9" s="17">
+      <c r="G9" s="1">
         <v>45631</v>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="3">
         <v>45813</v>
       </c>
-      <c r="I9" s="19">
+      <c r="I9" s="6">
         <v>45813</v>
       </c>
     </row>
-    <row r="10" spans="2:9" ht="21" x14ac:dyDescent="0.25">
-      <c r="B10" s="10" t="s">
+    <row r="10" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="1">
         <v>44930</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="1">
         <v>45111</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="1">
         <v>45295</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="1">
         <v>45477</v>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="1">
         <v>45661</v>
       </c>
-      <c r="H10" s="18">
+      <c r="H10" s="3">
         <v>45842</v>
       </c>
-      <c r="I10" s="19">
+      <c r="I10" s="6">
         <v>46026</v>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="11" t="s">
+    <row r="11" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="1">
         <v>44958</v>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="1">
         <v>45139</v>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="1">
         <v>45323</v>
       </c>
-      <c r="F11" s="20">
+      <c r="F11" s="1">
         <v>45505</v>
       </c>
-      <c r="G11" s="21">
+      <c r="G11" s="2">
         <v>45689</v>
       </c>
-      <c r="H11" s="21">
+      <c r="H11" s="3">
         <v>45870</v>
       </c>
-      <c r="I11" s="22">
+      <c r="I11" s="6">
         <v>46054</v>
       </c>
     </row>
-    <row r="15" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="2:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="4" t="s">
+    <row r="12" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="1">
+        <v>45231</v>
+      </c>
+      <c r="D12" s="1">
+        <v>45413</v>
+      </c>
+      <c r="E12" s="1">
+        <v>45597</v>
+      </c>
+      <c r="F12" s="1">
+        <v>45778</v>
+      </c>
+      <c r="G12" s="2">
+        <v>45962</v>
+      </c>
+      <c r="H12" s="3">
+        <v>46143</v>
+      </c>
+      <c r="I12" s="6">
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="7">
+        <v>45658</v>
+      </c>
+      <c r="D13" s="7">
+        <v>45809</v>
+      </c>
+      <c r="E13" s="7">
+        <v>46023</v>
+      </c>
+      <c r="F13" s="7">
+        <v>46174</v>
+      </c>
+      <c r="G13" s="8">
+        <v>46388</v>
+      </c>
+      <c r="H13" s="9">
+        <v>46539</v>
+      </c>
+      <c r="I13" s="10">
+        <v>46753</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="15" spans="2:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C15" s="23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" ht="93.75" x14ac:dyDescent="0.3">
+      <c r="B16" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16" s="26"/>
+    </row>
+    <row r="17" spans="2:4" ht="56.25" x14ac:dyDescent="0.3">
+      <c r="B17" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" ht="112.5" x14ac:dyDescent="0.3">
+      <c r="B18" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" ht="131.25" x14ac:dyDescent="0.3">
+      <c r="B19" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" ht="112.5" x14ac:dyDescent="0.3">
+      <c r="B20" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" ht="112.5" x14ac:dyDescent="0.3">
+      <c r="B21" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" s="28"/>
+    </row>
+    <row r="22" spans="2:4" ht="56.25" x14ac:dyDescent="0.3">
+      <c r="B22" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" ht="112.5" x14ac:dyDescent="0.3">
+      <c r="B23" s="27" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="2:6" ht="110.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6" t="s">
+      <c r="C23" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="29"/>
+    </row>
+    <row r="24" spans="2:4" ht="169.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="F17" s="16"/>
-    </row>
-    <row r="18" spans="2:6" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6" ht="262.5" x14ac:dyDescent="0.25">
-      <c r="B20" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6" t="s">
+      <c r="C24" s="25" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="B21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6" ht="93.75" x14ac:dyDescent="0.25">
-      <c r="B22" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="7"/>
-    </row>
-    <row r="23" spans="2:6" ht="93.75" x14ac:dyDescent="0.25">
-      <c r="B23" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="954542bb-2825-439d-9db6-a5c04d3b21fd" xsi:nil="true"/>
-    <orden xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010039E554BA5E2FA5449283D399C0FD5B7C" ma:contentTypeVersion="22" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="c12b387725171b57bce8d20228431399">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c" xmlns:ns3="954542bb-2825-439d-9db6-a5c04d3b21fd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0b67a6e2ff3c9ebaa3c6cdc8923b4bdc" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010039E554BA5E2FA5449283D399C0FD5B7C" ma:contentTypeVersion="22" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="99316247900046118e13a249c2e2a979">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c" xmlns:ns3="954542bb-2825-439d-9db6-a5c04d3b21fd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="18ff31ee8df8f768b70ea272e17d0ebc" ns2:_="" ns3:_="">
     <xsd:import namespace="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
     <xsd:import namespace="954542bb-2825-439d-9db6-a5c04d3b21fd"/>
     <xsd:element name="properties">
@@ -1138,7 +1250,7 @@
                 <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:orden"/>
+                <xsd:element ref="ns2:orden" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -1225,7 +1337,7 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="orden" ma:index="26" ma:displayName="orden" ma:format="Dropdown" ma:internalName="orden" ma:percentage="FALSE">
+    <xsd:element name="orden" ma:index="26" nillable="true" ma:displayName="orden" ma:format="Dropdown" ma:internalName="orden" ma:percentage="FALSE">
       <xsd:simpleType>
         <xsd:restriction base="dms:Number">
           <xsd:maxInclusive value="12"/>
@@ -1374,7 +1486,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -1383,7 +1495,46 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="954542bb-2825-439d-9db6-a5c04d3b21fd" xsi:nil="true"/>
+    <orden xmlns="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{070F46FF-6A46-467B-9374-33A76BCB1EEF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="cc851cf5-9d25-4af0-b62f-d23d0a4f5e5c"/>
+    <ds:schemaRef ds:uri="954542bb-2825-439d-9db6-a5c04d3b21fd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E56B48B9-8D50-4C8A-A3A8-779F015C9076}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CD7FD21-EF15-47EF-BE64-355A321DA262}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -1392,16 +1543,4 @@
     <ds:schemaRef ds:uri="954542bb-2825-439d-9db6-a5c04d3b21fd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A81B8B19-5EF1-41AD-B48A-DAF88D404038}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E56B48B9-8D50-4C8A-A3A8-779F015C9076}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>